--- a/Configs/Excel/CfgGacha.xlsx
+++ b/Configs/Excel/CfgGacha.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\DreamTileNew\Configs\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935FA9C0-31FF-41F6-A302-0CD8BAACFE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gacha" sheetId="1" r:id="rId1"/>
@@ -200,14 +206,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,345 +228,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -574,256 +251,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -846,61 +281,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1150,29 +541,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="6" width="24.4336283185841" customWidth="1"/>
+    <col min="3" max="6" width="24.453125" customWidth="1"/>
     <col min="7" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="17.1238938053097" customWidth="1"/>
-    <col min="10" max="10" width="16.8761061946903" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.90625" style="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="12" width="22.1238938053097" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1238938053097" style="1" customWidth="1"/>
-    <col min="14" max="15" width="16.8761061946903" style="1" customWidth="1"/>
-    <col min="16" max="16" width="15.8761061946903" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16.6283185840708" customWidth="1"/>
+    <col min="12" max="12" width="22.08984375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" style="1" customWidth="1"/>
+    <col min="14" max="15" width="16.90625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.90625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:17">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:17">
+    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -1278,7 +669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:17">
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1331,7 +722,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" ht="13.85" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1</v>
@@ -1379,10 +770,10 @@
         <v>1</v>
       </c>
       <c r="Q4" s="1">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="5" ht="13.85" spans="1:17">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>2</v>
@@ -1430,72 +821,72 @@
         <v>2</v>
       </c>
       <c r="Q5" s="1">
-        <v>2497</v>
-      </c>
-    </row>
-    <row r="6" ht="13.85" spans="1:17">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" ht="13.85" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" ht="13.85" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" ht="13.85" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" ht="13.85" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" ht="13.85" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" ht="13.85" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" ht="13.85" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="15" ht="13.85" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" ht="13.85" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Configs/Excel/CfgGacha.xlsx
+++ b/Configs/Excel/CfgGacha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\DreamTileNew\Configs\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935FA9C0-31FF-41F6-A302-0CD8BAACFE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4213A6E-EEDA-4CDC-A6D1-9AC5A6F7B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>5;6</t>
   </si>
   <si>
-    <t>79;21</t>
-  </si>
-  <si>
     <t>1;3;5;7;9</t>
   </si>
   <si>
@@ -201,13 +198,17 @@
   </si>
   <si>
     <t>2497;2499;2500;2502;2503;2505;2506;2507;2508;2509;2510;2511;2512;2513;2514;2515;2516;2517;2518;2519;2520;2521;2522;2523;2524;2525;2526;2527;2528;2529;2530;2531;2532;2533;2534;2535;2536;2537;2538;2539;2540;2541;2542;2543;2544;2545;2546;2547;2548;2549;2550;2551;2552;2553;2554;2555;2556;2557;2558;2559;2560;2561;2562;2563;2564;2565;2566;2567;2568;2569;2570;2571;2572;2573;2574;2575;2576;2577;2578;2579;2580;2581;2582;2583;2584;2585;2586;2587;2588;2589;2590;2591;2592;2593;2594;2595;2596;2597;2598;2599;2600;2601;2602;2603;2604;2605;2606;2607;2608;2609;2610;2611;2612;2613;2614;2615;2616;2617;2618;2619;2621;2622;2623;2624;2625;2626;2627;2628;2629;2630;2631;2632;2633;2634;2635;2636;2637;2638;2639;2640;2641;2642;2643;2644;2645;2646;2647;2648;2649;2650;2651;2652;2653;2654;2655;2656;2657;2658;2659;2660;2661;2662;2663;2664;2665;2666;2667;2668;2669;2670;2671;2672;2673;2674;2675;2676;2677;2678;2679;2680;2681;2682;2683;2684;2685;2686;2687;2688;2689;2690;2691;2692;2693;2694;2695;2696;2697;2698;2699;2700;2701;2702;2703;2704;2705;2706;2707;2708;2709;2710;2711;2712;2713;2714;2715;2716;2717;2718;2719;2720;2721;2722;2723;2724;2725;2726;2727;2728;2729;2730;2731;2732;2733;2734;2735;2736;2737;2738;2739;2740;2741;2742;2743;2744;2745;2746;2747;2748;2749;2750;2751;2752;2753;2754;2755;2756;2757;2758;2759;2760;2761;2762;2763;2764;2765;2766;2767;2768;2769;2770;2771;2772;2773;2774;2775;2776;2777;2778;2779;2780;2781;2782;2783;2784;2785;2786;2787;2788;2789;2790;2791;2792;2793;2794;2795;2796;2797;2798;2799;2800;2801;2802;2803;2804;2805;2806;2807;2808;2809;2810;2811;2812;2813;2814;2815;2816</t>
+  </si>
+  <si>
+    <t>100;0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +230,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -257,7 +266,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -279,6 +288,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,8 +754,8 @@
       <c r="G4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>45</v>
+      <c r="H4" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="I4" s="1">
         <v>10</v>
@@ -761,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="P4" s="1">
         <v>1</v>
@@ -779,22 +791,22 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="I5" s="1">
         <v>10</v>
@@ -812,10 +824,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="P5" s="1">
         <v>2</v>
